--- a/artfynd/A 31416-2024 artfynd.xlsx
+++ b/artfynd/A 31416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118903756</v>
+        <v>118903759</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>90500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751891</v>
+        <v>751887</v>
       </c>
       <c r="R2" t="n">
-        <v>7121271</v>
+        <v>7121285</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118903755</v>
+        <v>118903758</v>
       </c>
       <c r="B3" t="n">
-        <v>90469</v>
+        <v>90451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751551</v>
+        <v>751661</v>
       </c>
       <c r="R3" t="n">
-        <v>7121335</v>
+        <v>7121384</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118903757</v>
+        <v>118903755</v>
       </c>
       <c r="B4" t="n">
-        <v>79594</v>
+        <v>90469</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751767</v>
+        <v>751551</v>
       </c>
       <c r="R4" t="n">
-        <v>7121391</v>
+        <v>7121335</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118903758</v>
+        <v>118903761</v>
       </c>
       <c r="B5" t="n">
-        <v>90451</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751661</v>
+        <v>751623</v>
       </c>
       <c r="R5" t="n">
-        <v>7121384</v>
+        <v>7121336</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118903759</v>
+        <v>118903757</v>
       </c>
       <c r="B7" t="n">
-        <v>90500</v>
+        <v>79594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751887</v>
+        <v>751767</v>
       </c>
       <c r="R7" t="n">
-        <v>7121285</v>
+        <v>7121391</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118903761</v>
+        <v>118903756</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751623</v>
+        <v>751891</v>
       </c>
       <c r="R8" t="n">
-        <v>7121336</v>
+        <v>7121271</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 31416-2024 artfynd.xlsx
+++ b/artfynd/A 31416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118903759</v>
+        <v>118903756</v>
       </c>
       <c r="B2" t="n">
-        <v>90500</v>
+        <v>90511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751887</v>
+        <v>751891</v>
       </c>
       <c r="R2" t="n">
-        <v>7121285</v>
+        <v>7121271</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118903758</v>
+        <v>118903755</v>
       </c>
       <c r="B3" t="n">
-        <v>90451</v>
+        <v>90476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751661</v>
+        <v>751551</v>
       </c>
       <c r="R3" t="n">
-        <v>7121384</v>
+        <v>7121335</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118903755</v>
+        <v>118903761</v>
       </c>
       <c r="B4" t="n">
-        <v>90469</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751551</v>
+        <v>751623</v>
       </c>
       <c r="R4" t="n">
-        <v>7121335</v>
+        <v>7121336</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118903761</v>
+        <v>118903760</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751623</v>
+        <v>751536</v>
       </c>
       <c r="R5" t="n">
-        <v>7121336</v>
+        <v>7121261</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118903760</v>
+        <v>118903757</v>
       </c>
       <c r="B6" t="n">
-        <v>90522</v>
+        <v>79601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751536</v>
+        <v>751767</v>
       </c>
       <c r="R6" t="n">
-        <v>7121261</v>
+        <v>7121391</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118903757</v>
+        <v>118903758</v>
       </c>
       <c r="B7" t="n">
-        <v>79594</v>
+        <v>90458</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751767</v>
+        <v>751661</v>
       </c>
       <c r="R7" t="n">
-        <v>7121391</v>
+        <v>7121384</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118903756</v>
+        <v>118903759</v>
       </c>
       <c r="B8" t="n">
-        <v>90504</v>
+        <v>90507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751891</v>
+        <v>751887</v>
       </c>
       <c r="R8" t="n">
-        <v>7121271</v>
+        <v>7121285</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 31416-2024 artfynd.xlsx
+++ b/artfynd/A 31416-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118903756</v>
+        <v>118903760</v>
       </c>
       <c r="B2" t="n">
-        <v>90511</v>
+        <v>90529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751891</v>
+        <v>751536</v>
       </c>
       <c r="R2" t="n">
-        <v>7121271</v>
+        <v>7121261</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118903755</v>
+        <v>118903761</v>
       </c>
       <c r="B3" t="n">
-        <v>90476</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751551</v>
+        <v>751623</v>
       </c>
       <c r="R3" t="n">
-        <v>7121335</v>
+        <v>7121336</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118903761</v>
+        <v>118903759</v>
       </c>
       <c r="B4" t="n">
-        <v>78491</v>
+        <v>90507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751623</v>
+        <v>751887</v>
       </c>
       <c r="R4" t="n">
-        <v>7121336</v>
+        <v>7121285</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118903760</v>
+        <v>118903755</v>
       </c>
       <c r="B5" t="n">
-        <v>90529</v>
+        <v>90476</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751536</v>
+        <v>751551</v>
       </c>
       <c r="R5" t="n">
-        <v>7121261</v>
+        <v>7121335</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118903759</v>
+        <v>118903756</v>
       </c>
       <c r="B8" t="n">
-        <v>90507</v>
+        <v>90511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751887</v>
+        <v>751891</v>
       </c>
       <c r="R8" t="n">
-        <v>7121285</v>
+        <v>7121271</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
